--- a/LubanData/Data/#game.Weapon.xlsx
+++ b/LubanData/Data/#game.Weapon.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R03175b58b7274020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R140ebccbe3a2400f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -445,6 +445,9 @@
       <x:c r="D5">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="E5" t="str">
+        <x:v>弹弓</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="B6">
@@ -455,6 +458,9 @@
       </x:c>
       <x:c r="D6">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>弓箭</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -466,6 +472,114 @@
       </x:c>
       <x:c r="D7">
         <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>普通法杖</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8"/>
+      <x:c r="B8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>火法杖</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9"/>
+      <x:c r="B9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>冰法杖</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10"/>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>雷法杖</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>火冰法杖</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>火雷法杖</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>冰雷法杖</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>火冰雷法杖</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/LubanData/Data/#game.Weapon.xlsx
+++ b/LubanData/Data/#game.Weapon.xlsx
@@ -1366,7 +1366,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1380,7 +1380,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -1394,7 +1394,7 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1408,7 +1408,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1436,7 +1436,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -1450,7 +1450,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -1464,7 +1464,7 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>9</v>
